--- a/资源/数据/新闻/news_library_text_only.xlsx
+++ b/资源/数据/新闻/news_library_text_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,55 +449,60 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>摘要</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>正文</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>现象总结</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>趋势预测</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>正文末尾提示</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>默认方向</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>可选方向</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>默认强度</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>可选强度</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>反向逻辑说明</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>底层接口参数</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -532,55 +537,60 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>央行维持谨慎观望，利率方向暂不明朗</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>{time_text}，{region}政策层维持谨慎口风，市场对后续利率动作的判断暂未统一。汇率短线大概率还是围绕政策预期反复摆动，不会因为一句话就完全改写方向。 若后续通胀继续顽固，相关货币更容易获得支撑；若增长突然转弱，政策口风也可能转向保守。 这类消息的关键，不在表态本身有多强硬，而在利率上的优势会不会被市场继续放大。</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>{time_text}，{region}政策层维持谨慎口风，市场对后续利率动作的判断暂未统一。汇率短线大概率还是围绕政策预期反复摆动，不会因为一句话就完全改写方向。</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>若后续通胀继续顽固，相关货币更容易获得支撑；若增长突然转弱，政策口风也可能转向保守。</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>这类消息的关键，不在表态本身有多强硬，而在利率上的优势会不会被市场继续放大。</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>震荡</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>震荡|走稳|偏强</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>轻微</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>若市场认为表态比预期更强或更弱，方向都可能偏离原有震荡判断。</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>policy_signal|expectation_hold</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>官员讲话|政策观察</t>
         </is>
@@ -615,55 +625,60 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>议息临近市场趋于谨慎，方向等待决议落地</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>{time_text}，议息窗口临近，市场主动压缩了对激进政策变化的押注幅度。价格短线看似平静，但本质上更像是在等待下一次明确表态来决定方向。 若会议结果略超预期，相关货币容易迅速脱离当前区间；若结果平淡，盘面可能继续维持试探式震荡。 这类新闻真正该盯的，是市场预期有没有提前收敛，以及利率路径上的想象空间是不是正在变窄。</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>{time_text}，议息窗口临近，市场主动压缩了对激进政策变化的押注幅度。价格短线看似平静，但本质上更像是在等待下一次明确表态来决定方向。</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>若会议结果略超预期，相关货币容易迅速脱离当前区间；若结果平淡，盘面可能继续维持试探式震荡。</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>这类新闻真正该盯的，是市场预期有没有提前收敛，以及利率路径上的想象空间是不是正在变窄。</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>等待</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>等待|震荡|收敛</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>轻微</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>轻微|普通</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>若市场突然提前收到更明确风向，等待状态也可能立刻被打破。</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>expectation_hold|volatility_hold</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>议息前瞻|押注收敛|等待区间</t>
         </is>
@@ -698,55 +713,60 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>就业消费信号矛盾，市场方向判断分裂</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>{time_text}，最新数据没有给出特别明确的方向，部分席位认为经济仍有韧性，也有人担心后劲不足。相关货币短期更像是在等待新的确认，而不是立刻选择单边突破。 若后续数据仍旧忽强忽弱，汇率大概率维持反复拉锯；若连续出现同方向信号，市场判断才会逐渐统一。 数据类资讯最值得盯的，是经济基本面有没有变差，以及市场给出的合理价格区间是否开始下移。</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>{time_text}，最新数据没有给出特别明确的方向，部分席位认为经济仍有韧性，也有人担心后劲不足。相关货币短期更像是在等待新的确认，而不是立刻选择单边突破。</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>若后续数据仍旧忽强忽弱，汇率大概率维持反复拉锯；若连续出现同方向信号，市场判断才会逐渐统一。</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>数据类资讯最值得盯的，是经济基本面有没有变差，以及市场给出的合理价格区间是否开始下移。</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>分化</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>分化|震荡|承压</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>轻微</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>若后续席位迅速统一判断，分化状态也可能很快变成单边承压或企稳。</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>expectation_split</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>就业|消费|分歧</t>
         </is>
@@ -781,55 +801,60 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>制造业景气度来回摆动，复苏共识难以形成</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>{time_text}，制造业景气度没有持续给出同方向信号，市场对{region}后续复苏节奏的判断出现来回摆动。汇率层面也因此更容易陷入上不去、跌不深的拉锯状态。 若景气指标持续改善，相关货币有机会慢慢修复估值；若订单与产出再度走弱，市场会更快转向保守。 这类数据后面最该盯的，是基本面修复有没有真正站稳，以及市场对合理价格水平的判断会不会继续下移。</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>{time_text}，制造业景气度没有持续给出同方向信号，市场对{region}后续复苏节奏的判断出现来回摆动。汇率层面也因此更容易陷入上不去、跌不深的拉锯状态。</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>若景气指标持续改善，相关货币有机会慢慢修复估值；若订单与产出再度走弱，市场会更快转向保守。</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>这类数据后面最该盯的，是基本面修复有没有真正站稳，以及市场对合理价格水平的判断会不会继续下移。</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>震荡</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>震荡|修复|承压</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>若修复线索变得连续，方向可从震荡转成修复；若负面信号集中出现，也可能转成持续承压。</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>fair_value_drift|expectation_shift</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>制造业|复苏分歧|景气反复</t>
         </is>
@@ -864,55 +889,60 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>多头试探性进场，企稳信号尚需确认</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>{time_text}，多头情绪略有回暖，不过追价意愿还不算坚决。价格层面更像是在试探底部是否稳住，而不是所有资金都相信反弹已经真正开始。 若后续消息继续温和偏暖，企稳判断有机会逐步强化；若再有利空打断，当前乐观预期也可能迅速退潮。 这类新闻更要看市场信心是不是持续恢复，而不是只看一两次短线反弹。</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>{time_text}，多头情绪略有回暖，不过追价意愿还不算坚决。价格层面更像是在试探底部是否稳住，而不是所有资金都相信反弹已经真正开始。</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>若后续消息继续温和偏暖，企稳判断有机会逐步强化；若再有利空打断，当前乐观预期也可能迅速退潮。</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>这类新闻更要看市场信心是不是持续恢复，而不是只看一两次短线反弹。</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>走稳</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>走稳|回暖|震荡</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>轻微</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>若后续利空突然增加，走稳判断会迅速退化成震荡甚至回吐。</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>sentiment_up_small|expectation_probe</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>企稳预期|试探押注</t>
         </is>
@@ -947,55 +977,60 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>交易席位收缩仓位，乐观预期出现动摇</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>{time_text}，原本偏乐观的交易席位开始主动收缩仓位，市场对{region}货币继续走强的把握明显下降。价格虽然未必立刻转空，但原本顺畅的上行动能看起来已经不像之前那样牢固。 若后续催化继续缺席，相关货币更可能进入高位震荡甚至温和回吐；若新的利好重新出现，乐观押注也可能再度聚集。 这类预期新闻真正反映的，是市场信心有没有松动，以及追价资金是否开始变得保守。</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>{time_text}，原本偏乐观的交易席位开始主动收缩仓位，市场对{region}货币继续走强的把握明显下降。价格虽然未必立刻转空，但原本顺畅的上行动能看起来已经不像之前那样牢固。</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>若后续催化继续缺席，相关货币更可能进入高位震荡甚至温和回吐；若新的利好重新出现，乐观押注也可能再度聚集。</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>这类预期新闻真正反映的，是市场信心有没有松动，以及追价资金是否开始变得保守。</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>回吐</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>回吐|震荡|分化</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>若市场重新获得新催化，回吐判断也可能反转成走稳甚至再度偏强。</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>expectation_down_small|sentiment_down_small</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>乐观降温|仓位收缩|预期回吐</t>
         </is>
@@ -1030,55 +1065,60 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>商品与订单双重波动，出口前景蒙阴</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>{time_text}，商品价格与海外订单信号不够稳定，市场对{region}出口链条的持续性仍有保留。汇率层面更可能先表现为温和承压，而不是立刻出现急跌。 若商品价格继续回落或订单持续走弱，相关货币中期更容易慢慢转弱；若外需恢复，这类压力也可能被逐步消化。 贸易类新闻真正影响的，是外部需求有没有转差，以及长期支撑汇率的基本盘是否被削弱。</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>{time_text}，商品价格与海外订单信号不够稳定，市场对{region}出口链条的持续性仍有保留。汇率层面更可能先表现为温和承压，而不是立刻出现急跌。</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>若商品价格继续回落或订单持续走弱，相关货币中期更容易慢慢转弱；若外需恢复，这类压力也可能被逐步消化。</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>贸易类新闻真正影响的，是外部需求有没有转差，以及长期支撑汇率的基本盘是否被削弱。</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>承压</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>承压|偏弱|震荡</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>若市场认为订单波动只是阶段扰动，方向也可能保持震荡而不是继续偏弱。</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>trade_bias_down_small</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>订单|出口|商品</t>
         </is>
@@ -1113,55 +1153,60 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>原材料价格反复，产业链成本压力累积</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>{time_text}，原材料价格的反复波动让市场开始重新估算{region}产业链的成本压力。汇率不会因为单次报价就立刻变脸，但中期竞争力的想象空间确实被压缩了一些。 若成本压力继续累积，相关货币的中期支撑可能逐步削弱；若价格回稳，市场也会把这次扰动视作短期波折。 这类产业新闻背后真正要看的，是出口环境有没有转差，以及长期支撑汇率的基本盘会不会被慢慢侵蚀。</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>{time_text}，原材料价格的反复波动让市场开始重新估算{region}产业链的成本压力。汇率不会因为单次报价就立刻变脸，但中期竞争力的想象空间确实被压缩了一些。</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>若成本压力继续累积，相关货币的中期支撑可能逐步削弱；若价格回稳，市场也会把这次扰动视作短期波折。</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>这类产业新闻背后真正要看的，是出口环境有没有转差，以及长期支撑汇率的基本盘会不会被慢慢侵蚀。</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>偏弱</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>偏弱|承压|震荡</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>若原材料波动很快回落，成本压力缓解后也可能只留下短暂噪音。</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>trade_bias_shift|fair_value_drift</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>原材料|成本压力|产业评估</t>
         </is>
@@ -1196,55 +1241,60 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>强硬外交信号压低风险偏好</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>{time_text}，最新表态没有直接改变政策，但已经足以让交易席位提高警惕。相关汇率未必马上单边变化，不过短线资金通常会先降低风险暴露。 若后续言辞继续升级，避险交易可能进一步升温；若局势很快缓和，当前冲击也可能只停留在情绪层面。 时政类新闻最后还是要看市场情绪是否继续恶化，以及避险买盘有没有持续放大。</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>{time_text}，最新表态没有直接改变政策，但已经足以让交易席位提高警惕。相关汇率未必马上单边变化，不过短线资金通常会先降低风险暴露。</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>若后续言辞继续升级，避险交易可能进一步升温；若局势很快缓和，当前冲击也可能只停留在情绪层面。</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>时政类新闻最后还是要看市场情绪是否继续恶化，以及避险买盘有没有持续放大。</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>降温</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>降温|承压|震荡</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>轻微</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>若局势很快缓和，市场可能把它视作口头噪音，方向会从降温转回平稳。</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>sentiment_down_small|safe_haven_up_small</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>外交摩擦|风险偏好</t>
         </is>
@@ -1279,55 +1329,60 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>止损盘集中引爆，价格波动连锁放大</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>{time_text}，原本分散的卖压在关键价位附近集中释放，市场开始出现连锁止损。这样的走势通常更偏向短线情绪宣泄，不一定意味着中期判断已经被彻底改写。 若后续对手盘不足，波动可能继续扩大；若恐慌卖压快速衰减，价格也可能很快出现技术性修正。 盘面异动最后真正要看的，是短线波动会不会继续蔓延，以及市场深度是否恢复到正常水平。</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>{time_text}，原本分散的卖压在关键价位附近集中释放，市场开始出现连锁止损。这样的走势通常更偏向短线情绪宣泄，不一定意味着中期判断已经被彻底改写。</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>若后续对手盘不足，波动可能继续扩大；若恐慌卖压快速衰减，价格也可能很快出现技术性修正。</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>盘面异动最后真正要看的，是短线波动会不会继续蔓延，以及市场深度是否恢复到正常水平。</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>放大</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>放大|偏移|收敛</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>明显</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>普通|明显|剧烈</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>若恐慌卖压被快速承接，放大走势也可能很快转成修正或收敛。</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>volatility_spike|liquidity_tighten|sentiment_down_small</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>止损链|恐慌波动|技术性修正</t>
         </is>
@@ -1362,55 +1417,60 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>数据走软叠加鸽派信号，宽松押注激增</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>{time_text}，经济数据走软叠加官员偏鸽表态，市场开始提前押注{region}后续可能转向更宽松的方向。汇率短线承受一定压力，但市场也清楚——宽松预期未必次次都能兑现。 若宽松信号继续累积，相关货币可能逐步转入承压；若数据意外走强或官员回撤表态，宽松押注也会快速降温。 这类行情的核心，是市场到底是在赌真宽松，还是只是在消化短期情绪。</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>{time_text}，经济数据走软叠加官员偏鸽表态，市场开始提前押注{region}后续可能转向更宽松的方向。汇率短线承受一定压力，但市场也清楚——宽松预期未必次次都能兑现。</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>若宽松信号继续累积，相关货币可能逐步转入承压；若数据意外走强或官员回撤表态，宽松押注也会快速降温。</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>这类行情的核心，是市场到底是在赌真宽松，还是只是在消化短期情绪。</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>承压</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>承压|偏弱|震荡</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>若市场提前计价过度，宽松预期反而可能被修正，方向从承压转成企稳。</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>rate_diff_down|expectation_down</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>宽松预期|收益率|政策转向</t>
         </is>
@@ -1445,55 +1505,60 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>消费端数据低迷，内需对增长的支撑趋弱</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>{time_text}，最新消费端数据没达到市场此前的预估，部分机构开始怀疑{region}的内需能否继续撑住增长。汇率未必立刻大幅回调，但中期乐观的基础确实没那么稳了。 若消费持续走弱，相关货币更容易逐步转入偏弱；若下月数据明显回升，这一轮担忧也可能很快被放在一边。 消费类消息后面要看的是内需是不是真的在降温，以及市场对增长前景的修正会不会进一步加快。</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>{time_text}，最新消费端数据没达到市场此前的预估，部分机构开始怀疑{region}的内需能否继续撑住增长。汇率未必立刻大幅回调，但中期乐观的基础确实没那么稳了。</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>若消费持续走弱，相关货币更容易逐步转入偏弱；若下月数据明显回升，这一轮担忧也可能很快被放在一边。</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>消费类消息后面要看的是内需是不是真的在降温，以及市场对增长前景的修正会不会进一步加快。</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>承压</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>承压|偏弱|震荡</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>若市场原本已经预期数据偏弱，利空落地后也可能反而走企稳修复。</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>expectation_shift|fair_value_drift</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>消费|零售|增长放缓</t>
         </is>
@@ -1528,55 +1593,60 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>经济指标回暖，悲观预期出现松动</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>{time_text}，最新一轮经济指标较前期有所改善，交易席位开始讨论{region}是否正在走出疲软阶段。目前还远未到全面转乐观的时候，但至少悲观预期看起来没那么牢固了。 若改善趋势延续，相关货币有机会逐步走稳甚至修复；若数据很快再次转弱，当前回暖气氛也可能被迅速冲淡。 这种数据需要持续观察，关键不是单次好转，而是能不能连续给出正面信号。</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>{time_text}，最新一轮经济指标较前期有所改善，交易席位开始讨论{region}是否正在走出疲软阶段。目前还远未到全面转乐观的时候，但至少悲观预期看起来没那么牢固了。</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>若改善趋势延续，相关货币有机会逐步走稳甚至修复；若数据很快再次转弱，当前回暖气氛也可能被迅速冲淡。</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>这种数据需要持续观察，关键不是单次好转，而是能不能连续给出正面信号。</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>修复</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>修复|走稳|回暖</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>轻微</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>若好转被证实只是技术性反弹而非趋势改善，修复预期也可能很快转回承压。</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>expectation_up_small|fair_value_up_small</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>复苏苗头|数据改善|修复预期</t>
         </is>
@@ -1611,55 +1681,60 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>剧烈波动后市场归于平静，新平衡正在形成</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>{time_text}，此前大幅拉扯的行情开始逐渐平静，买卖盘的价差也在收窄。这样的盘面说明短线情绪正在消化，价格可能在当前位置试探一个新的平衡区间。 若收敛的同时成交量也在下降，说明市场在等下一个方向；若收敛后突然放量，方向选择可能很快出现。 收敛行情里最该盯的不是价格振幅，而是放量的时机——平静往往意味着下一轮波动的酝酿。</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>{time_text}，此前大幅拉扯的行情开始逐渐平静，买卖盘的价差也在收窄。这样的盘面说明短线情绪正在消化，价格可能在当前位置试探一个新的平衡区间。</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>若收敛的同时成交量也在下降，说明市场在等下一个方向；若收敛后突然放量，方向选择可能很快出现。</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>收敛行情里最该盯的不是价格振幅，而是放量的时机——平静往往意味着下一轮波动的酝酿。</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>收敛</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>收敛|等待|震荡</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>轻微</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>轻微|普通</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>若收敛期间累积了大量未被释放的方向押注，后续突破可能比预期更剧烈。</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>volatility_down_small|liquidity_recover</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>波动收敛|平衡区间|缩量</t>
         </is>
@@ -1694,55 +1769,60 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>出口数据回暖，贸易悲观预期松动</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>{time_text}，最新出口数据好于预期，市场开始讨论{region}的外部需求是不是比想象的更稳。汇率短期获得一定支撑，但要彻底扭转之前的谨慎判断，还需要更多正面信号来确认。 若出口改善持续，相关货币有机会逐步走稳甚至修复；若后续订单再次转弱，这一轮乐观情绪也会随之消退。 出口修复类新闻要看的是外需改善有没有持续性，而不是单月数据的偶然回暖。</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>{time_text}，最新出口数据好于预期，市场开始讨论{region}的外部需求是不是比想象的更稳。汇率短期获得一定支撑，但要彻底扭转之前的谨慎判断，还需要更多正面信号来确认。</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>若出口改善持续，相关货币有机会逐步走稳甚至修复；若后续订单再次转弱，这一轮乐观情绪也会随之消退。</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>出口修复类新闻要看的是外需改善有没有持续性，而不是单月数据的偶然回暖。</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>修复</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>修复|走稳|回暖</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>若市场认为数据受益于短期外部因素而非趋势改善，乐观情绪也可能很快被消化。</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>trade_bias_up_small|expectation_up_small</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>出口修复|贸易改善|外需回暖</t>
         </is>
@@ -1777,55 +1857,60 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>商品价格同步上涨，资源出口收入看好</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>{time_text}，能源与原材料价格同步上涨，市场开始调高对{region}资源出口收入的相关预期。汇率短期更容易获得支撑，但如果涨得太快，市场也会担心价格泡沫会不会反过来压制需求。 若商品价格维持高位，相关货币继续保持韧性；若价格快速回落，出口收入预期也会跟着收缩。 商品类新闻后续要看的是价格上涨是需求真正拉动，还是只是短期资金炒作。</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>{time_text}，能源与原材料价格同步上涨，市场开始调高对{region}资源出口收入的相关预期。汇率短期更容易获得支撑，但如果涨得太快，市场也会担心价格泡沫会不会反过来压制需求。</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>若商品价格维持高位，相关货币继续保持韧性；若价格快速回落，出口收入预期也会跟着收缩。</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>商品类新闻后续要看的是价格上涨是需求真正拉动，还是只是短期资金炒作。</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>偏强</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>偏强|走稳|震荡</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>若商品价格上涨被市场解读成成本压力而非利好，方向可能从偏强转成震荡甚至承压。</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>trade_bias_shift|commodity_up</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>大宗商品|出口收入|资源货币</t>
         </is>
@@ -1860,55 +1945,60 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>友好表态安抚市场，短线担忧缓解</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>{time_text}，{region}高层公开表态倾向于通过对话解决问题，市场此前紧绷的神经略微放松。相关货币的短期压力有所减轻，但真正的转折还需要后续行动来验证——光靠说话是不够的。 若后续出台实质性的缓和措施，市场信心有机会继续修复；若表态后没有动作，当前缓解也可能只是一次短暂的情绪修复。 领导人表态好不好用，关键看后面能不能拿出实际行动——市场对空话的耐心有限。</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>{time_text}，{region}高层公开表态倾向于通过对话解决问题，市场此前紧绷的神经略微放松。相关货币的短期压力有所减轻，但真正的转折还需要后续行动来验证——光靠说话是不够的。</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>若后续出台实质性的缓和措施，市场信心有机会继续修复；若表态后没有动作，当前缓解也可能只是一次短暂的情绪修复。</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>领导人表态好不好用，关键看后面能不能拿出实际行动——市场对空话的耐心有限。</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>修复</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>修复|回暖|震荡</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>轻微</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>若后续被证实只是口头安抚而无实质跟进，市场可能重新回到之前的紧张状态。</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>sentiment_up_small|safe_haven_down_small</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>领导人表态|缓和信号|情绪修复</t>
         </is>
@@ -1943,55 +2033,60 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>多空在关键价位反复交锋，方向突破尚需催化</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>{time_text}，买盘和卖盘在同一个价位区间来回交锋，价格多次尝试突破但都无法站稳。市场暂时没有足够的合力去打破当前的僵持局面，短线交易的胜率也因此明显下降。 若某一方的资金开始明显占优，平衡可能被打破，价格朝突破方向移动；若僵持继续，盘面可能维持缩量拉锯——直到下一个催化出现。 反复拉锯的时候耐心比方向判断更重要——先倒下去的那一方，往往就是下一段走势的反方向。</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>{time_text}，买盘和卖盘在同一个价位区间来回交锋，价格多次尝试突破但都无法站稳。市场暂时没有足够的合力去打破当前的僵持局面，短线交易的胜率也因此明显下降。</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>若某一方的资金开始明显占优，平衡可能被打破，价格朝突破方向移动；若僵持继续，盘面可能维持缩量拉锯——直到下一个催化出现。</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>反复拉锯的时候耐心比方向判断更重要——先倒下去的那一方，往往就是下一段走势的反方向。</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>拉锯</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>拉锯|震荡|等待</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>若拉锯期间某一方悄悄积累了大量头寸，后续突破的力度可能远超预期。</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>volatility_hold|expectation_split</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>反复拉锯|关键价位|平衡之战</t>
         </is>
@@ -2026,55 +2121,60 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>过渡期政策真空，资金先行收缩</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>{time_text}，{region}政坛进入过渡期，新政府的政策方向和组阁进度存在较大不确定性。市场暂时无法判断后续经济路线会怎么走，短线资金通常会先收缩风险敞口，等更清晰的信息出现再做决定。 若过渡进程顺利且新政府延续现有路线，市场情绪可能很快修复；若组阁僵持或政策方向出现大幅摇摆，相关货币的疲软状态可能延续更久。 过渡期的不确定性往往被市场提前计价——好消息是等到尘埃落定时，反而可能利空出尽。</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>{time_text}，{region}政坛进入过渡期，新政府的政策方向和组阁进度存在较大不确定性。市场暂时无法判断后续经济路线会怎么走，短线资金通常会先收缩风险敞口，等更清晰的信息出现再做决定。</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>若过渡进程顺利且新政府延续现有路线，市场情绪可能很快修复；若组阁僵持或政策方向出现大幅摇摆，相关货币的疲软状态可能延续更久。</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>过渡期的不确定性往往被市场提前计价——好消息是等到尘埃落定时，反而可能利空出尽。</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>承压</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>承压|震荡|偏弱</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>普通</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>若过渡政府超预期稳定或延续原有政策方向，承压判断也可能转成企稳。</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>sentiment_down_small|policy_signal</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>过渡政府|政治不确定性|政策观望</t>
         </is>
@@ -2109,55 +2209,60 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>经济数据大幅走弱，紧急宽松预期升温</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>{time_text}，最新经济数据大幅弱于预期，市场开始讨论{region}可能被迫提前采取宽松措施。汇率短线迅速走弱，但市场也清楚——紧急宽松本身说明经济出了问题，不完全是利好出尽的问题。 若数据持续恶化且政策转弯加速，相关货币中期可能继续承压；若宽松预期已提前到位，也可能出现利空出尽式的短期修复。 紧急宽松的行情里，市场最矛盾的地方在于——政策放水短期打压汇率，但长期也可能帮经济托底。</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>{time_text}，最新经济数据大幅弱于预期，市场开始讨论{region}可能被迫提前采取宽松措施。汇率短线迅速走弱，但市场也清楚——紧急宽松本身说明经济出了问题，不完全是利好出尽的问题。</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>若数据持续恶化且政策转弯加速，相关货币中期可能继续承压；若宽松预期已提前到位，也可能出现利空出尽式的短期修复。</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>紧急宽松的行情里，市场最矛盾的地方在于——政策放水短期打压汇率，但长期也可能帮经济托底。</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>偏弱</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>偏弱|承压|震荡</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>明显</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>普通|明显|剧烈</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>若市场认为宽松预期已计价充分，实际落地后可能出现利空出尽式的修复反弹。</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>rate_diff_down|expectation_down</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>宽松预期|紧急政策|经济恶化</t>
         </is>
@@ -2192,55 +2297,60 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>服务业景气回升，经济结构转型曙光初现</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>{time_text}，最新服务业相关指标显示活动有所回暖，市场开始讨论{region}经济结构是否正在从制造业承压向服务业拉动过渡。目前信号还不算强，但至少不是一边倒的悲观了。 若服务业修复持续并带动就业和消费，相关货币有机会逐步企稳；若服务业回暖被证明只是季节性波动，市场会很快回到原来的判断中。 服务业修复比制造业更贴近内需——如果服务消费真的起来了，对经济的支撑会更稳一些。</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>{time_text}，最新服务业相关指标显示活动有所回暖，市场开始讨论{region}经济结构是否正在从制造业承压向服务业拉动过渡。目前信号还不算强，但至少不是一边倒的悲观了。</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>若服务业修复持续并带动就业和消费，相关货币有机会逐步企稳；若服务业回暖被证明只是季节性波动，市场会很快回到原来的判断中。</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>服务业修复比制造业更贴近内需——如果服务消费真的起来了，对经济的支撑会更稳一些。</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>修复</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>修复|走稳|回暖</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>轻微</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>轻微|普通|明显</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>若服务业修复背后是短期促销或季节性因素，市场可能很快修正回暖预期。</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>expectation_up_small|fair_value_up_small</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>服务业|PMI|经济结构改善</t>
         </is>
